--- a/data/valuations/ITX_MC/ITX_MC_modelo_valoracion.xlsx
+++ b/data/valuations/ITX_MC/ITX_MC_modelo_valoracion.xlsx
@@ -551,47 +551,47 @@
     <row r="4">
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2026</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY2027</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY2028</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY2029</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY2030</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>FY2030</t>
+          <t>FY2031</t>
         </is>
       </c>
     </row>
@@ -619,16 +619,16 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>27716</v>
+        <v>32569</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>32569</v>
+        <v>35947</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>35947</v>
+        <v>38631.875</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>38632</v>
+        <v>39864.173</v>
       </c>
     </row>
     <row r="8">
@@ -638,19 +638,19 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.0441</v>
+        <v>0.055</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.03920000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.0343</v>
+        <v>0.05</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>0.0294</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="9">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.079</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.0711</v>
+        <v>0.075</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.05529999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>0.0474</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="10">
@@ -682,19 +682,19 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.0171</v>
+        <v>0.02</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.0152</v>
+        <v>0.025</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.0133</v>
+        <v>0.03</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0.0114</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="11">
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.5740841427180992</v>
+        <v>0.58</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.5740841427180992</v>
+        <v>0.58</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.5740841427180992</v>
+        <v>0.58</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.5740841427180992</v>
+        <v>0.58</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0.5740841427180992</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.5940841427180992</v>
+        <v>0.59</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.5940841427180992</v>
+        <v>0.59</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.5940841427180992</v>
+        <v>0.59</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.5940841427180992</v>
+        <v>0.59</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0.5940841427180992</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +819,19 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.5540841427180991</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.5540841427180991</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.5540841427180991</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.5540841427180991</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0.5540841427180991</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.09860970745209235</v>
+        <v>0.095</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.09860970745209235</v>
+        <v>0.095</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.09860970745209235</v>
+        <v>0.095</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.09860970745209235</v>
+        <v>0.095</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.09860970745209235</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.08860970745209236</v>
+        <v>0.09</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.08860970745209236</v>
+        <v>0.09</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.08860970745209236</v>
+        <v>0.09</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.08860970745209236</v>
+        <v>0.09</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.08860970745209236</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1086097074520923</v>
+        <v>0.095</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.1086097074520923</v>
+        <v>0.095</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1086097074520923</v>
+        <v>0.095</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1086097074520923</v>
+        <v>0.095</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.1086097074520923</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="23">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1005,19 +1005,19 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.08653999983109634</v>
+        <v>0.083</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.08653999983109634</v>
+        <v>0.083</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.08653999983109634</v>
+        <v>0.083</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.08653999983109634</v>
+        <v>0.083</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.08653999983109634</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="31">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.05132867549803267</v>
+        <v>0.06</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.05132867549803267</v>
+        <v>0.06</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.05132867549803267</v>
+        <v>0.06</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.05132867549803267</v>
+        <v>0.06</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.05132867549803267</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="32">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.21548627634832</v>
+        <v>0.22</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.21548627634832</v>
+        <v>0.22</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.21548627634832</v>
+        <v>0.22</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.21548627634832</v>
+        <v>0.22</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.21548627634832</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="34">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0828</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1128</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2026</t>
         </is>
       </c>
     </row>
@@ -1298,16 +1298,16 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>27716</v>
+        <v>32569</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>32569</v>
+        <v>35947</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>35947</v>
+        <v>38631.875</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>38632</v>
+        <v>39864.173</v>
       </c>
     </row>
     <row r="7">
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>11902</v>
+        <v>14011</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>14011</v>
+        <v>15186</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>15186</v>
+        <v>16288.488</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>16288</v>
+        <v>16641.718</v>
       </c>
     </row>
     <row r="8">
@@ -1336,16 +1336,16 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>15814</v>
+        <v>18559</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>18559</v>
+        <v>20762</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>20762</v>
+        <v>22343.387</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>22343</v>
+        <v>23222.455</v>
       </c>
     </row>
     <row r="9">
@@ -1355,16 +1355,16 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.5705729542502526</v>
+        <v>0.5698363474469588</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>0.5698363474469588</v>
+        <v>0.5775725373466493</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0.5775725373466493</v>
+        <v>0.5783666208280079</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>0.5783547318285359</v>
+        <v>0.5825394897819653</v>
       </c>
     </row>
     <row r="11">
@@ -1393,16 +1393,16 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3030</v>
+        <v>3105</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3105</v>
+        <v>3368</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3368</v>
+        <v>3712</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>3712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1412,16 +1412,16 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>4282</v>
+        <v>5895</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>5895</v>
+        <v>6914</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>6914</v>
+        <v>7593.512</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>7673</v>
+        <v>8045.112</v>
       </c>
     </row>
     <row r="14">
@@ -1431,16 +1431,16 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.15449559821042</v>
+        <v>0.181000337744481</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>0.181000337744481</v>
+        <v>0.1923387208946505</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>0.1923387208946505</v>
+        <v>0.1965607933862905</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.1986177262373162</v>
+        <v>0.2018130916700567</v>
       </c>
     </row>
     <row r="16">
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>144</v>
+        <v>271</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>271</v>
+        <v>352.191</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>353</v>
+        <v>370.314</v>
       </c>
     </row>
     <row r="17">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>949</v>
+        <v>1211</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1211</v>
+        <v>1475</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1475</v>
+        <v>1700.263</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1700</v>
+        <v>1799.624</v>
       </c>
     </row>
     <row r="18">
@@ -1488,16 +1488,16 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>3243</v>
+        <v>4130</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>4130</v>
+        <v>5381</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>5381</v>
+        <v>5866.133</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>5866</v>
+        <v>6220.09</v>
       </c>
     </row>
     <row r="19">
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>0.1170082262952807</v>
+        <v>0.1268077005741656</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>0.1268077005741656</v>
+        <v>0.1496926029988594</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0.1496926029988594</v>
+        <v>0.1518469657504328</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.1518430316835784</v>
+        <v>0.1560320842476777</v>
       </c>
     </row>
     <row r="21">
@@ -1526,16 +1526,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>7231</v>
+        <v>8278</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>8278</v>
+        <v>10038</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>10038</v>
+        <v>11103.105</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>10946</v>
+        <v>11660.075</v>
       </c>
     </row>
     <row r="22">
@@ -1545,16 +1545,16 @@
         </is>
       </c>
       <c r="C22" s="11" t="n">
-        <v>0.2608962332226872</v>
+        <v>0.2541680739353373</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>0.2541680739353373</v>
+        <v>0.2792444432080563</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>0.2792444432080563</v>
+        <v>0.2874078723851742</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>0.2833402360737213</v>
+        <v>0.2924950932758595</v>
       </c>
     </row>
     <row r="23">
@@ -1564,16 +1564,16 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1.042</v>
+        <v>1.326</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>1.326</v>
+        <v>1.726</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>1.726</v>
+        <v>1.88</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>1.881</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1583,16 +1583,16 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>2848</v>
+        <v>2776</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>2776</v>
+        <v>2897</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2897</v>
+        <v>3173.984</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2997</v>
+        <v>3270.047</v>
       </c>
     </row>
     <row r="27">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>7021</v>
+        <v>5561</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>5561</v>
+        <v>7007</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>7007</v>
+        <v>6382</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>6382</v>
+        <v>5276.288</v>
       </c>
     </row>
     <row r="29">
@@ -1633,16 +1633,16 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>13602</v>
+        <v>14639</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>14639</v>
+        <v>16016</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>16016</v>
+        <v>16356</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>16356</v>
+        <v>15691.243</v>
       </c>
     </row>
     <row r="30">
@@ -1652,16 +1652,16 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>12704</v>
+        <v>12501</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>12501</v>
+        <v>13434</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>13434</v>
+        <v>15274</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>15274</v>
+        <v>11135.303</v>
       </c>
     </row>
     <row r="31">
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>196</v>
+        <v>196.727</v>
       </c>
     </row>
     <row r="32">
@@ -1690,16 +1690,16 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>28945</v>
+        <v>29983</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>29983</v>
+        <v>32735</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>32735</v>
+        <v>34714</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>34714</v>
+        <v>35638.312</v>
       </c>
     </row>
     <row r="34">
@@ -1709,16 +1709,16 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>8030</v>
+        <v>8137</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>8137</v>
+        <v>8937</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>8937</v>
+        <v>10187</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>10187</v>
+        <v>10171.916</v>
       </c>
     </row>
     <row r="35">
@@ -1728,16 +1728,16 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>6014</v>
+        <v>5596</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>5596</v>
+        <v>5739</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>5739</v>
+        <v>5909</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>5909</v>
+        <v>1.711</v>
       </c>
     </row>
     <row r="36">
@@ -1747,16 +1747,16 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>13186</v>
+        <v>12950</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>12950</v>
+        <v>14063</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>14063</v>
+        <v>15038</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>15038</v>
+        <v>15243.153</v>
       </c>
     </row>
     <row r="38">
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>15759</v>
+        <v>17033</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>17033</v>
+        <v>18672</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>18672</v>
+        <v>19676</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>19676</v>
+        <v>20395.159</v>
       </c>
     </row>
     <row r="41">
@@ -1797,16 +1797,16 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>6754</v>
+        <v>6674</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>6674</v>
+        <v>8667</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>8667</v>
+        <v>9288.084000000001</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>9288</v>
+        <v>9231.932000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1816,16 +1816,16 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>-1126</v>
+        <v>-1415</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>-1415</v>
+        <v>-1872</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>-1872</v>
+        <v>-2671.848</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>-2672</v>
+        <v>-2711.857</v>
       </c>
     </row>
     <row r="44">
@@ -1835,16 +1835,16 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>5628</v>
+        <v>5259</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>5259</v>
+        <v>6795</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>6795</v>
+        <v>6616.236</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>6616</v>
+        <v>6520.075</v>
       </c>
     </row>
     <row r="46">
@@ -1854,16 +1854,16 @@
         </is>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2848</v>
+        <v>2776</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2776</v>
+        <v>2897</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>2897</v>
+        <v>3173.984</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>2997</v>
+        <v>3270.047</v>
       </c>
     </row>
     <row r="47">
@@ -1892,16 +1892,16 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>223</v>
+        <v>-669</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>-669</v>
+        <v>-56</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>-56</v>
+        <v>-197.793</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>-198</v>
+        <v>-802.525</v>
       </c>
     </row>
   </sheetData>
@@ -1968,47 +1968,47 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2025</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2026</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>FY2026</t>
+          <t>FY2027</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>FY2027</t>
+          <t>FY2028</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>FY2028</t>
+          <t>FY2029</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>FY2029</t>
+          <t>FY2030</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>FY2030</t>
+          <t>FY2031</t>
         </is>
       </c>
     </row>
@@ -2063,16 +2063,16 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>27716</v>
+        <v>32569</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>32569</v>
+        <v>35947</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>35947</v>
+        <v>38631.875</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>38632</v>
+        <v>39864.173</v>
       </c>
       <c r="G8" s="8">
         <f>Assumptions!G12</f>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>11902</v>
+        <v>14011</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>14011</v>
+        <v>15186</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>15186</v>
+        <v>16288.488</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>16288</v>
+        <v>16641.718</v>
       </c>
       <c r="G16" s="8">
         <f>-G15*(1-Assumptions!G18)</f>
@@ -2408,16 +2408,16 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>3030</v>
+        <v>3105</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>3105</v>
+        <v>3368</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3368</v>
+        <v>3712</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>3712</v>
+        <v>0</v>
       </c>
       <c r="G20" s="8">
         <f>-G15*Assumptions!G24</f>
@@ -2486,16 +2486,16 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>2848</v>
+        <v>2776</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>2776</v>
+        <v>2897</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2897</v>
+        <v>3173.984</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>2997</v>
+        <v>3270.047</v>
       </c>
       <c r="G22" s="8">
         <f>-G15*Assumptions!G32</f>
@@ -2697,31 +2697,31 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>144</v>
+        <v>271</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>271</v>
+        <v>352.191</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>353</v>
+        <v>370.314</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>353</v>
+        <v>370.314</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>353</v>
+        <v>370.314</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>353</v>
+        <v>370.314</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>353</v>
+        <v>370.314</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>353</v>
+        <v>370.314</v>
       </c>
     </row>
     <row r="30">
@@ -2774,16 +2774,16 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>949</v>
+        <v>1211</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1211</v>
+        <v>1475</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1475</v>
+        <v>1700.263</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1700</v>
+        <v>1799.624</v>
       </c>
       <c r="G31" s="8">
         <f>-ABS(G30)*Assumptions!G34</f>
@@ -3002,16 +3002,16 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>223</v>
+        <v>-669</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>-669</v>
+        <v>-56</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>-56</v>
+        <v>-197.793</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>-198</v>
+        <v>-802.525</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0</v>
@@ -3079,16 +3079,16 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>-1126</v>
+        <v>-1415</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>-1415</v>
+        <v>-1872</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-1872</v>
+        <v>-2671.848</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-2672</v>
+        <v>-2711.857</v>
       </c>
       <c r="G42" s="8">
         <f>-ABS(G15)*Assumptions!G33</f>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>52.74</v>
+        <v>48.48</v>
       </c>
     </row>
     <row r="4">
@@ -3295,19 +3295,19 @@
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="5">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>473</v>
+        <v>5274.577</v>
       </c>
     </row>
     <row r="30">
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>3116.167768</v>
+        <v>3114.766768</v>
       </c>
     </row>
     <row r="33">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/52.74-1</f>
+        <f>C33/48.48-1</f>
         <v/>
       </c>
     </row>
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>8x</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>12x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>12x</t>
+          <t>14x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>14x</t>
+          <t>16x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>16x</t>
+          <t>18x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.05500000000000001</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*8/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*10/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*10/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*12/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*12/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*14/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*16/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*18/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.07279999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*8/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*10/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*10/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*12/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*12/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*14/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*16/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*18/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0828</v>
+        <v>0.07500000000000001</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*8/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*10/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*10/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*12/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*12/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*14/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*16/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*18/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*8/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*10/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*10/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*12/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*12/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*14/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*16/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*18/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1028</v>
+        <v>0.095</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*8/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*10/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*10/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*12/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*12/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*14/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*16/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*18/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1128</v>
+        <v>0.105</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*8/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*10/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*10/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*12/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*12/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*14/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*16/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*18/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1228</v>
+        <v>0.115</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*8/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*10/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*10/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*12/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*12/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*14/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*16/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*18/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
